--- a/data/trans_dic/IP41-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,3; 94,34</t>
+          <t>83,73; 93,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,93; 96,84</t>
+          <t>87,24; 96,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,27; 91,26</t>
+          <t>78,69; 90,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,64; 96,61</t>
+          <t>88,86; 97,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,16; 97,69</t>
+          <t>89,63; 97,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,83; 92,77</t>
+          <t>81,37; 92,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,91; 94,41</t>
+          <t>88,0; 94,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90,63; 96,63</t>
+          <t>90,43; 96,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82,41; 90,61</t>
+          <t>82,65; 90,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>87,42; 96,85</t>
+          <t>87,79; 96,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,85; 93,94</t>
+          <t>83,47; 93,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,04; 87,52</t>
+          <t>75,51; 88,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,14; 97,87</t>
+          <t>89,78; 97,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,04; 93,3</t>
+          <t>82,56; 93,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,61; 92,36</t>
+          <t>81,74; 92,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90,85; 96,57</t>
+          <t>90,0; 96,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85,19; 92,58</t>
+          <t>85,23; 92,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80,55; 88,52</t>
+          <t>80,62; 88,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,21; 98,94</t>
+          <t>89,91; 98,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,05; 96,83</t>
+          <t>87,58; 96,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,5; 96,56</t>
+          <t>85,11; 96,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85,67; 95,07</t>
+          <t>85,55; 95,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,41; 97,19</t>
+          <t>87,72; 96,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,78; 96,2</t>
+          <t>85,61; 95,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89,6; 96,04</t>
+          <t>89,95; 95,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89,96; 96,28</t>
+          <t>89,62; 96,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87,24; 95,28</t>
+          <t>87,28; 95,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,2</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,53; 93,57</t>
+          <t>86,9; 93,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,05; 91,76</t>
+          <t>84,79; 92,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,44; 85,63</t>
+          <t>77,3; 85,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,28; 93,21</t>
+          <t>86,39; 92,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,59; 89,87</t>
+          <t>82,39; 89,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,76; 87,05</t>
+          <t>78,77; 87,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,56; 92,56</t>
+          <t>87,62; 92,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84,6; 90,01</t>
+          <t>84,7; 89,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,13; 85,22</t>
+          <t>79,11; 85,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>81,55; 92,06</t>
+          <t>81,51; 92,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,44; 87,68</t>
+          <t>77,09; 87,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,69; 87,64</t>
+          <t>76,56; 87,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>89,08; 96,34</t>
+          <t>89,4; 96,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,8; 88,09</t>
+          <t>77,56; 88,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,91; 86,9</t>
+          <t>75,4; 86,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,95; 93,71</t>
+          <t>87,37; 93,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79,38; 86,54</t>
+          <t>79,53; 86,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78,22; 86,14</t>
+          <t>78,19; 85,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82,65; 94,49</t>
+          <t>83,49; 94,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,66; 94,29</t>
+          <t>80,15; 94,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,9; 90,58</t>
+          <t>73,93; 89,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,02; 93,99</t>
+          <t>83,47; 94,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77,5; 90,81</t>
+          <t>77,3; 90,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,31; 77,4</t>
+          <t>58,72; 77,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84,98; 93,13</t>
+          <t>84,8; 93,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81,5; 91,13</t>
+          <t>81,02; 91,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69,39; 81,52</t>
+          <t>69,3; 81,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,01</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,82; 92,56</t>
+          <t>88,89; 92,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,5; 90,58</t>
+          <t>86,77; 90,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,13; 85,74</t>
+          <t>81,3; 85,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,0; 93,43</t>
+          <t>90,18; 93,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,92; 89,87</t>
+          <t>85,6; 89,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,39; 86,19</t>
+          <t>81,51; 86,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>90,13; 92,71</t>
+          <t>90,15; 92,55</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86,82; 89,65</t>
+          <t>86,8; 89,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82,01; 85,44</t>
+          <t>81,99; 85,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>92161</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>84062</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>70960</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90784</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84932</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88043</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>182944</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>168995</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>159003</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>85998; 96530</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>78462; 87101</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>65379; 75293</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>86138; 94165</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>80452; 87718</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>81203; 92751</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>175686; 188617</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>162509; 173280</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>151161; 165732</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>79849</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>83467</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>86053</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81685</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85987</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98433</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>161534</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>169453</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>184486</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>75562; 83082</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>77851; 87540</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>79142; 92494</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>77186; 84077</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>79898; 90226</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>91627; 103821</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>154831; 165533</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>161972; 175440</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>174871; 192978</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>64960</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>80564</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56958</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90767</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81183</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>69361</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>155728</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>161747</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>126319</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>60589; 66676</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75453; 83445</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52635; 59838</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>84983; 94444</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>76218; 84204</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>64574; 72307</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>149971; 160026</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>155082; 166544</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>119812; 130688</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>179986</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>182457</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>182874</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>178927</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>196870</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>174497</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>358914</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>379326</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>357371</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>172738; 185625</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174760; 189678</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>172822; 191375</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>171787; 184855</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>187931; 204405</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>165591; 183206</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>348403; 367708</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>367792; 389947</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>343189; 369903</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>88991</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>123820</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>112825</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>117302</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>117876</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>116634</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>206292</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>241695</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>229459</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>82498; 93140</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>114990; 129992</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>104276; 119657</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>112107; 121242</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>109405; 124528</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>107894; 124094</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>197996; 212423</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>230825; 251574</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>218360; 239950</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>67286</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>47993</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>51094</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>64900</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>62813</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>46634</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>132186</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>110806</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>97728</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>62510; 70812</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>43207; 50676</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>45162; 54847</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>60429; 68240</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>57232; 67213</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>39827; 52465</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>124872; 137284</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>103660; 116630</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>89341; 105074</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>573234</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>602362</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>560763</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>624365</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>629662</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>593602</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1197599</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1232024</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1154365</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>560942; 584537</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>588752; 615407</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>545196; 576258</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>612204; 635373</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>613412; 642976</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>577451; 609860</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1180908; 1212282</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1210981; 1250546</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1130719; 1175932</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP41-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -519,15 +519,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -632,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -664,47 +640,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>86,94%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,73; 93,98</t>
+          <t>83,79; 93,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,24; 96,85</t>
+          <t>87,32; 96,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,69; 90,62</t>
+          <t>77,67; 91,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,69; 96,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,86; 97,15</t>
+          <t>89,27; 97,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,63; 97,72</t>
+          <t>82,19; 93,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,37; 92,94</t>
+          <t>87,82; 94,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,68; 96,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88,0; 94,48</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>90,43; 96,43</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>82,65; 90,62</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>82,51; 90,68</t>
         </is>
       </c>
     </row>
@@ -804,47 +750,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89,17%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
           <t>85,05%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>87,79; 96,53</t>
+          <t>86,34; 96,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,47; 93,86</t>
+          <t>83,6; 94,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,51; 88,25</t>
+          <t>75,63; 87,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,71; 97,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,78; 97,8</t>
+          <t>82,31; 93,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,56; 93,23</t>
+          <t>81,94; 92,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,74; 92,62</t>
+          <t>90,61; 96,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,52; 92,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90,0; 96,22</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>85,23; 92,32</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>80,62; 88,97</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>80,46; 88,7</t>
         </is>
       </c>
     </row>
@@ -944,47 +860,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>93,47%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>92,02%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -997,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,91; 98,94</t>
+          <t>89,57; 98,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,58; 96,85</t>
+          <t>87,75; 96,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,11; 96,76</t>
+          <t>84,61; 96,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,47; 95,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85,55; 95,08</t>
+          <t>87,88; 96,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,72; 96,91</t>
+          <t>85,42; 96,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,61; 95,86</t>
+          <t>89,66; 96,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89,58; 96,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89,95; 95,98</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>89,62; 96,24</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87,28; 95,21</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>87,11; 95,0</t>
         </is>
       </c>
     </row>
@@ -1084,47 +970,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>87,36%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>82,38%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,9; 93,39</t>
+          <t>86,74; 93,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,79; 92,03</t>
+          <t>84,18; 91,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,3; 85,6</t>
+          <t>77,02; 85,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,91; 93,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,39; 92,97</t>
+          <t>82,25; 90,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,39; 89,61</t>
+          <t>78,67; 87,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,77; 87,15</t>
+          <t>87,71; 92,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,2; 89,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,62; 92,48</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>84,7; 89,81</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>79,11; 85,27</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>79,47; 85,13</t>
         </is>
       </c>
     </row>
@@ -1224,47 +1080,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>83,28%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
           <t>82,16%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>81,51; 92,02</t>
+          <t>82,18; 92,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,09; 87,14</t>
+          <t>77,25; 87,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,56; 87,86</t>
+          <t>76,82; 87,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,77; 96,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>89,4; 96,68</t>
+          <t>78,04; 88,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,56; 88,28</t>
+          <t>75,03; 86,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,4; 86,73</t>
+          <t>87,79; 93,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>79,52; 86,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,37; 93,74</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>79,53; 86,68</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>78,19; 85,92</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>78,26; 85,59</t>
         </is>
       </c>
     </row>
@@ -1364,47 +1190,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>86,6%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
           <t>75,81%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,49; 94,58</t>
+          <t>83,03; 94,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,15; 94,0</t>
+          <t>80,51; 95,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,93; 89,78</t>
+          <t>75,31; 90,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82,79; 93,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,47; 94,26</t>
+          <t>77,12; 90,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77,3; 90,78</t>
+          <t>59,38; 77,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,72; 77,35</t>
+          <t>85,08; 93,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,93; 90,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84,8; 93,22</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81,02; 91,15</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>69,3; 81,51</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>68,27; 81,45</t>
         </is>
       </c>
     </row>
@@ -1504,47 +1300,32 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>88,31%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
           <t>83,71%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,89; 92,63</t>
+          <t>88,77; 92,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,77; 90,7</t>
+          <t>86,85; 90,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,3; 85,93</t>
+          <t>81,09; 85,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,22; 93,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,18; 93,59</t>
+          <t>85,72; 89,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,6; 89,72</t>
+          <t>81,43; 85,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,51; 86,08</t>
+          <t>90,23; 92,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,98; 89,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>90,15; 92,55</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>86,8; 89,63</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>81,99; 85,27</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>81,86; 85,19</t>
         </is>
       </c>
     </row>
@@ -1625,16 +1391,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1647,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1661,15 +1427,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1680,23 +1443,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1718,47 +1478,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1774,9 +1519,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1806,47 +1548,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>245</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>237</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1874,47 +1601,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90784</t>
+          <t>84932</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84932</t>
+          <t>88043</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88043</t>
+          <t>182944</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>168995</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>182944</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>168995</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
           <t>159003</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85998; 96530</t>
+          <t>86063; 96316</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78462; 87101</t>
+          <t>78530; 87214</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65379; 75293</t>
+          <t>64540; 75958</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85973; 93634</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>86138; 94165</t>
+          <t>80130; 87724</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80452; 87718</t>
+          <t>82025; 92881</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81203; 92751</t>
+          <t>175338; 188396</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>162941; 173180</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>175686; 188617</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>162509; 173280</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>151161; 165732</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>150895; 165850</t>
         </is>
       </c>
     </row>
@@ -2014,47 +1711,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>145</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>246</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
           <t>273</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2082,47 +1764,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81685</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81685</t>
+          <t>85987</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85987</t>
+          <t>98433</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98433</t>
+          <t>161534</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>169453</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>161534</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>169453</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>184486</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2135,62 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75562; 83082</t>
+          <t>74316; 83003</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77851; 87540</t>
+          <t>77967; 87753</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79142; 92494</t>
+          <t>79275; 91896</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77980; 84119</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77186; 84077</t>
+          <t>79661; 90109</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79898; 90226</t>
+          <t>91844; 103721</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91627; 103821</t>
+          <t>155888; 166120</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>160631; 175732</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>154831; 165533</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>161972; 175440</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>174871; 192978</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>174525; 192398</t>
         </is>
       </c>
     </row>
@@ -2222,47 +1874,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>102</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>235</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>190</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2290,47 +1927,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90767</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90767</t>
+          <t>81183</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81183</t>
+          <t>69361</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69361</t>
+          <t>155728</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161747</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>155728</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>161747</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
           <t>126319</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2343,62 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>60589; 66676</t>
+          <t>60363; 66676</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>75453; 83445</t>
+          <t>75604; 83371</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52635; 59838</t>
+          <t>52323; 59793</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84900; 94519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>84983; 94444</t>
+          <t>76362; 84228</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76218; 84204</t>
+          <t>64432; 72649</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64574; 72307</t>
+          <t>149476; 160963</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>155017; 166196</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>149971; 160026</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>155082; 166544</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>119812; 130688</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>119579; 130402</t>
         </is>
       </c>
     </row>
@@ -2430,47 +2037,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>269</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>248</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>541</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>544</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
           <t>528</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2498,47 +2090,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>178927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>178927</t>
+          <t>196870</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>196870</t>
+          <t>174497</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>174497</t>
+          <t>358914</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>379326</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>358914</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>379326</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
           <t>357371</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>172738; 185625</t>
+          <t>172415; 185926</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>174760; 189678</t>
+          <t>173510; 188475</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>172822; 191375</t>
+          <t>172190; 191212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>170823; 185039</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>171787; 184855</t>
+          <t>187614; 205505</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>187931; 204405</t>
+          <t>165371; 182993</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>165591; 183206</t>
+          <t>348734; 367961</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>365590; 389060</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>348403; 367708</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>367792; 389947</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>343189; 369903</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>344719; 369307</t>
         </is>
       </c>
     </row>
@@ -2638,47 +2200,32 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>164</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>340</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
           <t>334</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2706,47 +2253,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>117302</t>
+          <t>117876</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>117876</t>
+          <t>116634</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>116634</t>
+          <t>206292</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241695</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>206292</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>241695</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
           <t>229459</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82498; 93140</t>
+          <t>83174; 93843</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>114990; 129992</t>
+          <t>115234; 130014</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104276; 119657</t>
+          <t>104622; 119723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>111322; 120850</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>112107; 121242</t>
+          <t>110080; 124738</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>109405; 124528</t>
+          <t>107354; 123456</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>107894; 124094</t>
+          <t>198941; 212756</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>230775; 250670</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>197996; 212423</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>230825; 251574</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>218360; 239950</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>218573; 239026</t>
         </is>
       </c>
     </row>
@@ -2846,47 +2363,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>196</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
           <t>141</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2914,47 +2416,32 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64900</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>64900</t>
+          <t>62813</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62813</t>
+          <t>46634</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46634</t>
+          <t>132186</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110806</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>132186</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>110806</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
           <t>97728</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>62510; 70812</t>
+          <t>62163; 70758</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43207; 50676</t>
+          <t>43405; 51216</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45162; 54847</t>
+          <t>46005; 55031</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>59936; 68039</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>60429; 68240</t>
+          <t>57095; 67173</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>57232; 67213</t>
+          <t>40277; 52880</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39827; 52465</t>
+          <t>125294; 137436</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>103553; 116244</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>124872; 137284</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>103660; 116630</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>89341; 105074</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>88008; 105003</t>
         </is>
       </c>
     </row>
@@ -3054,47 +2526,32 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>898</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>852</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1767</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
           <t>1703</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -3122,47 +2579,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>624365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>624365</t>
+          <t>629662</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>629662</t>
+          <t>593602</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>593602</t>
+          <t>1197599</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1232024</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1197599</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1232024</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
           <t>1154365</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -3175,62 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>560942; 584537</t>
+          <t>560168; 584716</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>588752; 615407</t>
+          <t>589342; 615289</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>545196; 576258</t>
+          <t>543778; 574371</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>612473; 634932</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>612204; 635373</t>
+          <t>614307; 642988</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>613412; 642976</t>
+          <t>576864; 609141</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>577451; 609860</t>
+          <t>1181855; 1213586</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1213472; 1253037</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1180908; 1212282</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1210981; 1250546</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1130719; 1175932</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>1128903; 1174827</t>
         </is>
       </c>
     </row>
@@ -3243,15 +2670,15 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/IP41-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>93,66%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>88,22%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>89,73%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>93,47%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>85,4%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,79; 93,77</t>
+          <t>88,64; 96,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,32; 96,98</t>
+          <t>89,16; 97,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,67; 91,42</t>
+          <t>81,83; 92,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88,69; 96,6</t>
+          <t>84,3; 94,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,27; 97,73</t>
+          <t>87,93; 96,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,19; 93,07</t>
+          <t>78,27; 91,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,82; 94,37</t>
+          <t>87,91; 94,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,68; 96,37</t>
+          <t>90,63; 96,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82,51; 90,68</t>
+          <t>82,41; 90,61</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88,85%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>87,81%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>92,77%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>89,49%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>82,1%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>88,85%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>87,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,34; 96,44</t>
+          <t>90,14; 97,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,6; 94,09</t>
+          <t>83,04; 93,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,63; 87,68</t>
+          <t>81,61; 92,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90,71; 97,85</t>
+          <t>87,42; 96,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,31; 93,11</t>
+          <t>82,85; 93,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,94; 92,53</t>
+          <t>75,04; 87,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,61; 96,56</t>
+          <t>90,85; 96,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,52; 92,47</t>
+          <t>85,19; 92,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,46; 88,7</t>
+          <t>80,55; 88,52</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>91,38%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93,43%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>96,39%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>93,51%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>92,11%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,43%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,57; 98,94</t>
+          <t>85,67; 95,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,75; 96,77</t>
+          <t>87,41; 97,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,61; 96,69</t>
+          <t>85,78; 96,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,47; 95,15</t>
+          <t>89,21; 98,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,88; 96,94</t>
+          <t>88,05; 96,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,42; 96,32</t>
+          <t>84,5; 96,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,66; 96,54</t>
+          <t>89,6; 96,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89,58; 96,04</t>
+          <t>89,96; 96,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87,11; 95,0</t>
+          <t>87,24; 95,28</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>83,01%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>90,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>88,52%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>81,79%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>86,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,74; 93,54</t>
+          <t>86,28; 93,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,18; 91,44</t>
+          <t>82,59; 89,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,02; 85,52</t>
+          <t>78,76; 87,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,91; 93,06</t>
+          <t>86,53; 93,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,25; 90,09</t>
+          <t>84,05; 91,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,67; 87,05</t>
+          <t>77,44; 85,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,71; 92,54</t>
+          <t>87,56; 92,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,2; 89,6</t>
+          <t>84,6; 90,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79,47; 85,13</t>
+          <t>79,13; 85,22</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>93,54%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>81,51%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>87,92%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>83,01%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>82,84%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>83,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>81,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,18; 92,72</t>
+          <t>89,08; 96,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,25; 87,16</t>
+          <t>77,8; 88,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,82; 87,91</t>
+          <t>75,91; 86,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88,77; 96,37</t>
+          <t>81,55; 92,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>78,04; 88,43</t>
+          <t>77,44; 87,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,03; 86,28</t>
+          <t>76,69; 87,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,79; 93,89</t>
+          <t>87,95; 93,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,52; 86,37</t>
+          <t>79,38; 86,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>78,26; 85,59</t>
+          <t>78,22; 86,14</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>89,65%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>84,84%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>68,76%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>89,87%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>89,02%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>83,64%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>89,65%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,84%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,03; 94,51</t>
+          <t>83,02; 93,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,51; 95,0</t>
+          <t>77,5; 90,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,31; 90,09</t>
+          <t>59,31; 77,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82,79; 93,99</t>
+          <t>82,65; 94,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>77,12; 90,73</t>
+          <t>80,66; 94,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,38; 77,97</t>
+          <t>74,9; 90,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,08; 93,33</t>
+          <t>84,98; 93,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80,93; 90,85</t>
+          <t>81,5; 91,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,27; 81,45</t>
+          <t>69,39; 81,52</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>91,97%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>87,86%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>83,79%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>90,84%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>88,77%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>83,62%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>91,97%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,77; 92,66</t>
+          <t>90,0; 93,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,85; 90,68</t>
+          <t>85,92; 89,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,09; 85,65</t>
+          <t>81,39; 86,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90,22; 93,53</t>
+          <t>88,82; 92,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,72; 89,72</t>
+          <t>86,5; 90,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,43; 85,98</t>
+          <t>81,13; 85,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,23; 92,65</t>
+          <t>90,13; 92,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>86,98; 89,81</t>
+          <t>86,82; 89,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>81,86; 85,19</t>
+          <t>82,01; 85,44</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1538,27 +1538,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>108</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>90784</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>84932</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>88043</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>92161</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>84062</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>70960</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>90784</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>84932</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88043</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>86063; 96316</t>
+          <t>85925; 93642</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78530; 87214</t>
+          <t>80032; 87686</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64540; 75958</t>
+          <t>81668; 92580</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85973; 93634</t>
+          <t>86590; 96900</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>80130; 87724</t>
+          <t>79079; 87089</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82025; 92881</t>
+          <t>65032; 75826</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>175338; 188396</t>
+          <t>175509; 188492</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>162941; 173180</t>
+          <t>162861; 173650</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>150895; 165850</t>
+          <t>150716; 165712</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>128</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>81685</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85987</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>98433</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>79849</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>83467</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>86053</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>81685</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85987</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98433</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74316; 83003</t>
+          <t>77490; 84140</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77967; 87753</t>
+          <t>80365; 90295</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79275; 91896</t>
+          <t>91478; 103525</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77980; 84119</t>
+          <t>75244; 83359</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79661; 90109</t>
+          <t>77266; 87613</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91844; 103721</t>
+          <t>78655; 91738</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>155888; 166120</t>
+          <t>156299; 166141</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>160631; 175732</t>
+          <t>161897; 175942</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>174525; 192398</t>
+          <t>174714; 191997</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>88</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>90767</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>81183</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69361</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>64960</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>80564</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>56958</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>90767</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>81183</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>69361</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>60363; 66676</t>
+          <t>85094; 94439</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>75604; 83371</t>
+          <t>75950; 84449</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52323; 59793</t>
+          <t>64700; 72563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84900; 94519</t>
+          <t>60117; 66676</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>76362; 84228</t>
+          <t>75860; 83424</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64432; 72649</t>
+          <t>52255; 59712</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>149476; 160963</t>
+          <t>149377; 160122</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>155017; 166196</t>
+          <t>155676; 166601</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>119579; 130402</t>
+          <t>119753; 130789</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>280</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>178927</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>196870</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>174497</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>179986</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>182457</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>182874</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>178927</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>196870</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>174497</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>172415; 185926</t>
+          <t>171556; 185345</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>173510; 188475</t>
+          <t>188404; 204997</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>172190; 191212</t>
+          <t>165563; 182993</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>170823; 185039</t>
+          <t>172005; 185990</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>187614; 205505</t>
+          <t>173227; 189121</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>165371; 182993</t>
+          <t>173147; 191460</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>348734; 367961</t>
+          <t>348145; 368017</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>365590; 389060</t>
+          <t>367335; 390821</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>344719; 369307</t>
+          <t>343277; 369676</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>173</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>117302</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>117876</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>116634</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>88991</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>123820</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>112825</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>117302</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>117876</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>116634</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>83174; 93843</t>
+          <t>111712; 120812</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>115234; 130014</t>
+          <t>109742; 124261</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104622; 119723</t>
+          <t>108618; 124342</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111322; 120850</t>
+          <t>82538; 93177</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>110080; 124738</t>
+          <t>115509; 130793</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>107354; 123456</t>
+          <t>104446; 119360</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>198941; 212756</t>
+          <t>199299; 212350</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>230775; 250670</t>
+          <t>230389; 251157</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>218573; 239026</t>
+          <t>218453; 240586</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>74</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>64900</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>62813</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>46634</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>67286</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>47993</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>51094</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>64900</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>62813</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>46634</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>62163; 70758</t>
+          <t>60103; 68044</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43405; 51216</t>
+          <t>57378; 67234</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46005; 55031</t>
+          <t>40227; 52498</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59936; 68039</t>
+          <t>61881; 70747</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>57095; 67173</t>
+          <t>43486; 50831</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40277; 52880</t>
+          <t>45754; 55335</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>125294; 137436</t>
+          <t>125145; 137145</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>103553; 116244</t>
+          <t>104272; 116602</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>88008; 105003</t>
+          <t>89455; 105083</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>857</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>869</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>851</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>898</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>852</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>624365</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>629662</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>593602</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>573234</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>602362</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>560763</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>624365</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>629662</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>593602</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>560168; 584716</t>
+          <t>610993; 634262</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>589342; 615289</t>
+          <t>615728; 644009</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>543778; 574371</t>
+          <t>576598; 610600</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>612473; 634932</t>
+          <t>560509; 584099</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>614307; 642988</t>
+          <t>586938; 614635</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>576864; 609141</t>
+          <t>544087; 574952</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1181855; 1213586</t>
+          <t>1180612; 1214361</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1213472; 1253037</t>
+          <t>1211251; 1250813</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1128903; 1174827</t>
+          <t>1130955; 1178282</t>
         </is>
       </c>
     </row>
